--- a/rasdaman_tiling_audit.xlsx
+++ b/rasdaman_tiling_audit.xlsx
@@ -1571,7 +1571,7 @@
       </c>
       <c r="AG5" s="4" t="inlineStr">
         <is>
-          <t>sdom disagrees with DescribeCoverage extent; 2 distinct tile shapes in sample</t>
+          <t>sdom disagrees with DescribeCoverage extent; 5 distinct tile shapes in sample</t>
         </is>
       </c>
     </row>
@@ -2091,7 +2091,7 @@
       </c>
       <c r="AG9" s="4" t="inlineStr">
         <is>
-          <t>sdom disagrees with DescribeCoverage extent</t>
+          <t>sdom disagrees with DescribeCoverage extent; 7 distinct tile shapes in sample</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="AG10" s="4" t="inlineStr">
         <is>
-          <t>sdom disagrees with DescribeCoverage extent</t>
+          <t>sdom disagrees with DescribeCoverage extent; 7 distinct tile shapes in sample</t>
         </is>
       </c>
     </row>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="AG11" s="4" t="inlineStr">
         <is>
-          <t>sdom disagrees with DescribeCoverage extent; 2 distinct tile shapes in sample</t>
+          <t>sdom disagrees with DescribeCoverage extent; 9 distinct tile shapes in sample</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="AG35" s="4" t="inlineStr">
         <is>
-          <t>3 distinct tile shapes in sample</t>
+          <t>7 distinct tile shapes in sample</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>1,2,1,67,22,22</t>
+          <t>1,2,1,28,22,22</t>
         </is>
       </c>
       <c r="M41" s="7" t="n">
@@ -6275,10 +6275,10 @@
         </is>
       </c>
       <c r="T41" s="7" t="n">
-        <v>682.7</v>
+        <v>570.6</v>
       </c>
       <c r="U41" s="7" t="n">
-        <v>134.9</v>
+        <v>56.4</v>
       </c>
       <c r="V41" s="4" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         </is>
       </c>
       <c r="W41" s="7" t="n">
-        <v>682.7</v>
+        <v>570.6</v>
       </c>
       <c r="X41" s="4" t="inlineStr">
         <is>
@@ -6297,7 +6297,7 @@
         <v>49</v>
       </c>
       <c r="Z41" s="4" t="n">
-        <v>13.9</v>
+        <v>11.6</v>
       </c>
       <c r="AA41" s="4" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="AG41" s="4" t="inlineStr">
         <is>
-          <t>sdom disagrees with DescribeCoverage extent; 4 distinct tile shapes in sample</t>
+          <t>sdom disagrees with DescribeCoverage extent; 10 distinct tile shapes in sample</t>
         </is>
       </c>
     </row>
@@ -29890,17 +29890,17 @@
     <row r="214">
       <c r="A214" s="4" t="inlineStr">
         <is>
-          <t>alfresco_relative_flammability_30yr</t>
+          <t>tas_2km_historical_wcs</t>
         </is>
       </c>
       <c r="B214" s="4" t="inlineStr">
         <is>
-          <t>alfresco_relative_flammability_30yr</t>
+          <t>tas_2km_historical_wcs</t>
         </is>
       </c>
       <c r="C214" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>wcs</t>
         </is>
       </c>
       <c r="D214" s="4" t="inlineStr">
@@ -29908,66 +29908,62 @@
           <t>no</t>
         </is>
       </c>
-      <c r="E214" s="4" t="inlineStr">
-        <is>
-          <t>iem/alfresco/relative_flammability/ingest.json</t>
-        </is>
-      </c>
+      <c r="E214" s="4" t="inlineStr"/>
       <c r="F214" s="4" t="inlineStr">
         <is>
-          <t>era model scenario X Y</t>
+          <t>month year X Y</t>
         </is>
       </c>
       <c r="G214" s="4" t="inlineStr">
         <is>
-          <t>5,7,4,3650,2100</t>
+          <t>12,115,1186,3218</t>
         </is>
       </c>
       <c r="H214" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I214" s="4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J214" s="4" t="inlineStr"/>
       <c r="K214" s="4" t="inlineStr">
         <is>
-          <t>[0:0,0:0,0:0,0:65535,0:16]</t>
+          <t>[0:11,0:114,0:31,0:31]</t>
         </is>
       </c>
       <c r="L214" s="4" t="inlineStr">
         <is>
-          <t>1,1,1,3650,17</t>
+          <t>1,114,31,31</t>
         </is>
       </c>
       <c r="M214" s="7" t="n">
-        <v>14333</v>
+        <v>276311</v>
       </c>
       <c r="N214" s="8" t="n">
-        <v>4.292</v>
+        <v>63.202</v>
       </c>
       <c r="O214" s="8" t="n">
-        <v>3.513</v>
+        <v>238.46</v>
       </c>
       <c r="P214" s="8" t="n">
-        <v>1.717</v>
+        <v>63.202</v>
       </c>
       <c r="Q214" s="9" t="n">
-        <v>0.8185</v>
+        <v>3.773</v>
       </c>
       <c r="R214" s="8" t="n">
-        <v>1.797</v>
-      </c>
-      <c r="S214" s="10" t="inlineStr">
-        <is>
-          <t>clean</t>
+        <v>175.258</v>
+      </c>
+      <c r="S214" s="12" t="inlineStr">
+        <is>
+          <t>duplicate entries</t>
         </is>
       </c>
       <c r="T214" s="7" t="n">
-        <v>62050</v>
+        <v>1905.3</v>
       </c>
       <c r="U214" s="7" t="n">
-        <v>1</v>
+        <v>116.4</v>
       </c>
       <c r="V214" s="4" t="inlineStr">
         <is>
@@ -29975,18 +29971,18 @@
         </is>
       </c>
       <c r="W214" s="7" t="n">
-        <v>62050</v>
+        <v>1905.3</v>
       </c>
       <c r="X214" s="4" t="inlineStr">
         <is>
-          <t>ALIGNED [0:4, 0:6, 0:3, 0:85, 0:85] tile size 4141760</t>
+          <t>ALIGNED [0:11, 0:114, 0:14, 0:14] tile size 3726000</t>
         </is>
       </c>
       <c r="Y214" s="7" t="n">
-        <v>7396</v>
+        <v>225</v>
       </c>
       <c r="Z214" s="4" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="AA214" s="4" t="inlineStr">
         <is>
@@ -30012,19 +30008,19 @@
       </c>
       <c r="AG214" s="4" t="inlineStr">
         <is>
-          <t>7 distinct tile shapes in sample</t>
+          <t>sdom disagrees with DescribeCoverage extent; 13 distinct tile shapes in sample</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
         <is>
-          <t>mean_annual_dtr</t>
+          <t>alfresco_relative_flammability_30yr</t>
         </is>
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>mean_annual_dtr</t>
+          <t>alfresco_relative_flammability_30yr</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
@@ -30039,17 +30035,17 @@
       </c>
       <c r="E215" s="4" t="inlineStr">
         <is>
-          <t>arctic_eds/annual_mean_dtr/ingest.json</t>
+          <t>iem/alfresco/relative_flammability/ingest.json</t>
         </is>
       </c>
       <c r="F215" s="4" t="inlineStr">
         <is>
-          <t>model year X Y</t>
+          <t>era model scenario X Y</t>
         </is>
       </c>
       <c r="G215" s="4" t="inlineStr">
         <is>
-          <t>3,121,198,106</t>
+          <t>5,7,4,3650,2100</t>
         </is>
       </c>
       <c r="H215" s="4" t="n">
@@ -30061,31 +30057,31 @@
       <c r="J215" s="4" t="inlineStr"/>
       <c r="K215" s="4" t="inlineStr">
         <is>
-          <t>[0:0,0:0,0:4599,0:223]</t>
+          <t>[0:0,0:0,0:0,0:65535,0:16]</t>
         </is>
       </c>
       <c r="L215" s="4" t="inlineStr">
         <is>
-          <t>1,1,198,106</t>
+          <t>1,1,1,3650,17</t>
         </is>
       </c>
       <c r="M215" s="7" t="n">
-        <v>222</v>
+        <v>14333</v>
       </c>
       <c r="N215" s="8" t="n">
-        <v>0.03</v>
+        <v>4.292</v>
       </c>
       <c r="O215" s="8" t="n">
-        <v>0.018</v>
+        <v>3.513</v>
       </c>
       <c r="P215" s="8" t="n">
-        <v>0.018</v>
+        <v>1.717</v>
       </c>
       <c r="Q215" s="9" t="n">
-        <v>0.6061</v>
+        <v>0.8185</v>
       </c>
       <c r="R215" s="8" t="n">
-        <v>0</v>
+        <v>1.797</v>
       </c>
       <c r="S215" s="10" t="inlineStr">
         <is>
@@ -30093,7 +30089,7 @@
         </is>
       </c>
       <c r="T215" s="7" t="n">
-        <v>20988</v>
+        <v>62050</v>
       </c>
       <c r="U215" s="7" t="n">
         <v>1</v>
@@ -30104,18 +30100,18 @@
         </is>
       </c>
       <c r="W215" s="7" t="n">
-        <v>20988</v>
+        <v>62050</v>
       </c>
       <c r="X215" s="4" t="inlineStr">
         <is>
-          <t>ALIGNED [0:2, 0:120, 0:52, 0:52] tile size 4078668</t>
+          <t>ALIGNED [0:4, 0:6, 0:3, 0:85, 0:85] tile size 4141760</t>
         </is>
       </c>
       <c r="Y215" s="7" t="n">
-        <v>2809</v>
+        <v>7396</v>
       </c>
       <c r="Z215" s="4" t="n">
-        <v>7.5</v>
+        <v>8.4</v>
       </c>
       <c r="AA215" s="4" t="inlineStr">
         <is>
@@ -30141,24 +30137,24 @@
       </c>
       <c r="AG215" s="4" t="inlineStr">
         <is>
-          <t>4 distinct tile shapes in sample</t>
+          <t>7 distinct tile shapes in sample</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="4" t="inlineStr">
         <is>
-          <t>cmip6_indicators_cf_wms</t>
+          <t>mean_annual_dtr</t>
         </is>
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>cmip6_indicators_cf_wms</t>
+          <t>mean_annual_dtr</t>
         </is>
       </c>
       <c r="C216" s="4" t="inlineStr">
         <is>
-          <t>wms</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D216" s="4" t="inlineStr">
@@ -30168,57 +30164,53 @@
       </c>
       <c r="E216" s="4" t="inlineStr">
         <is>
-          <t>ardac/cmip6_indicators/ingest.json</t>
+          <t>arctic_eds/annual_mean_dtr/ingest.json</t>
         </is>
       </c>
       <c r="F216" s="4" t="inlineStr">
         <is>
-          <t>model scenario time lat lon</t>
+          <t>model year X Y</t>
         </is>
       </c>
       <c r="G216" s="4" t="inlineStr">
         <is>
-          <t>14,5,151,288,43</t>
+          <t>3,121,198,106</t>
         </is>
       </c>
       <c r="H216" s="4" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I216" s="4" t="n">
-        <v>48</v>
-      </c>
-      <c r="J216" s="4" t="inlineStr">
-        <is>
-          <t>ALIGNED [0:*, 0:*, 0:*, 0:*, 0:*] tile size 4194304</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="J216" s="4" t="inlineStr"/>
       <c r="K216" s="4" t="inlineStr">
         <is>
-          <t>[0:*,0:*,0:*,0:*,0:*]</t>
+          <t>[0:0,0:0,0:4599,0:223]</t>
         </is>
       </c>
       <c r="L216" s="4" t="inlineStr">
         <is>
-          <t>1,1,7,288,43</t>
+          <t>1,1,198,106</t>
         </is>
       </c>
       <c r="M216" s="7" t="n">
-        <v>1616</v>
+        <v>222</v>
       </c>
       <c r="N216" s="8" t="n">
-        <v>6.283</v>
+        <v>0.03</v>
       </c>
       <c r="O216" s="8" t="n">
-        <v>6.587</v>
+        <v>0.018</v>
       </c>
       <c r="P216" s="8" t="n">
-        <v>6.283</v>
+        <v>0.018</v>
       </c>
       <c r="Q216" s="9" t="n">
-        <v>1.0483</v>
+        <v>0.6061</v>
       </c>
       <c r="R216" s="8" t="n">
-        <v>0.304</v>
+        <v>0</v>
       </c>
       <c r="S216" s="10" t="inlineStr">
         <is>
@@ -30226,29 +30218,29 @@
         </is>
       </c>
       <c r="T216" s="7" t="n">
-        <v>12630</v>
+        <v>20988</v>
       </c>
       <c r="U216" s="7" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="V216" s="4" t="inlineStr">
         <is>
-          <t>map</t>
+          <t>point</t>
         </is>
       </c>
       <c r="W216" s="7" t="n">
-        <v>7</v>
+        <v>20988</v>
       </c>
       <c r="X216" s="4" t="inlineStr">
         <is>
-          <t>ALIGNED [0:0, 0:0, 0:0, 0:287, 0:42] tile size 594432</t>
+          <t>ALIGNED [0:2, 0:120, 0:52, 0:52] tile size 4078668</t>
         </is>
       </c>
       <c r="Y216" s="7" t="n">
-        <v>1</v>
+        <v>2809</v>
       </c>
       <c r="Z216" s="4" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AA216" s="4" t="inlineStr">
         <is>
@@ -30274,24 +30266,24 @@
       </c>
       <c r="AG216" s="4" t="inlineStr">
         <is>
-          <t>sdom disagrees with DescribeCoverage extent; 6 distinct tile shapes in sample</t>
+          <t>4 distinct tile shapes in sample</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
         <is>
-          <t>alfresco_vegetation_mode_statistic</t>
+          <t>cmip6_indicators_cf_wms</t>
         </is>
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>alfresco_vegetation_mode_statistic</t>
+          <t>cmip6_indicators_cf_wms</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>wms</t>
         </is>
       </c>
       <c r="D217" s="4" t="inlineStr">
@@ -30301,83 +30293,87 @@
       </c>
       <c r="E217" s="4" t="inlineStr">
         <is>
-          <t>iem/alfresco/mode_vegetation_type/ingest.json</t>
+          <t>ardac/cmip6_indicators/ingest.json</t>
         </is>
       </c>
       <c r="F217" s="4" t="inlineStr">
         <is>
-          <t>era model scenario X Y</t>
+          <t>model scenario time lat lon</t>
         </is>
       </c>
       <c r="G217" s="4" t="inlineStr">
         <is>
-          <t>4,6,4,3650,2100</t>
+          <t>14,5,151,288,43</t>
         </is>
       </c>
       <c r="H217" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I217" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="J217" s="4" t="inlineStr">
+        <is>
+          <t>ALIGNED [0:*, 0:*, 0:*, 0:*, 0:*] tile size 4194304</t>
+        </is>
+      </c>
+      <c r="K217" s="4" t="inlineStr">
+        <is>
+          <t>[0:*,0:*,0:*,0:*,0:*]</t>
+        </is>
+      </c>
+      <c r="L217" s="4" t="inlineStr">
+        <is>
+          <t>1,1,7,288,43</t>
+        </is>
+      </c>
+      <c r="M217" s="7" t="n">
+        <v>1616</v>
+      </c>
+      <c r="N217" s="8" t="n">
+        <v>6.283</v>
+      </c>
+      <c r="O217" s="8" t="n">
+        <v>6.587</v>
+      </c>
+      <c r="P217" s="8" t="n">
+        <v>6.283</v>
+      </c>
+      <c r="Q217" s="9" t="n">
+        <v>1.0483</v>
+      </c>
+      <c r="R217" s="8" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="S217" s="10" t="inlineStr">
+        <is>
+          <t>clean</t>
+        </is>
+      </c>
+      <c r="T217" s="7" t="n">
+        <v>12630</v>
+      </c>
+      <c r="U217" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="V217" s="4" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="W217" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="X217" s="4" t="inlineStr">
+        <is>
+          <t>ALIGNED [0:0, 0:0, 0:0, 0:287, 0:42] tile size 594432</t>
+        </is>
+      </c>
+      <c r="Y217" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="I217" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="J217" s="4" t="inlineStr"/>
-      <c r="K217" s="4" t="inlineStr">
-        <is>
-          <t>[0:0,0:0,0:0,0:65535,0:16]</t>
-        </is>
-      </c>
-      <c r="L217" s="4" t="inlineStr">
-        <is>
-          <t>1,1,1,3650,17</t>
-        </is>
-      </c>
-      <c r="M217" s="7" t="n">
-        <v>11777</v>
-      </c>
-      <c r="N217" s="8" t="n">
-        <v>2.943</v>
-      </c>
-      <c r="O217" s="8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P217" s="8" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Q217" s="9" t="n">
-        <v>0.9786</v>
-      </c>
-      <c r="R217" s="8" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S217" s="10" t="inlineStr">
-        <is>
-          <t>clean</t>
-        </is>
-      </c>
-      <c r="T217" s="7" t="n">
-        <v>62050</v>
-      </c>
-      <c r="U217" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V217" s="4" t="inlineStr">
-        <is>
-          <t>point</t>
-        </is>
-      </c>
-      <c r="W217" s="7" t="n">
-        <v>62050</v>
-      </c>
-      <c r="X217" s="4" t="inlineStr">
-        <is>
-          <t>ALIGNED [0:3, 0:5, 0:3, 0:103, 0:103] tile size 4153344</t>
-        </is>
-      </c>
-      <c r="Y217" s="7" t="n">
-        <v>10816</v>
-      </c>
       <c r="Z217" s="4" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="AA217" s="4" t="inlineStr">
         <is>
@@ -30403,19 +30399,19 @@
       </c>
       <c r="AG217" s="4" t="inlineStr">
         <is>
-          <t>7 distinct tile shapes in sample</t>
+          <t>sdom disagrees with DescribeCoverage extent; 6 distinct tile shapes in sample</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="4" t="inlineStr">
         <is>
-          <t>iem_cru_2km_taspr_seasonal</t>
+          <t>alfresco_vegetation_mode_statistic</t>
         </is>
       </c>
       <c r="B218" s="4" t="inlineStr">
         <is>
-          <t>iem_cru_2km_taspr_seasonal</t>
+          <t>alfresco_vegetation_mode_statistic</t>
         </is>
       </c>
       <c r="C218" s="4" t="inlineStr">
@@ -30430,17 +30426,17 @@
       </c>
       <c r="E218" s="4" t="inlineStr">
         <is>
-          <t>iem/tas_pr_2km/cru_seasonal_ingest.json</t>
+          <t>iem/alfresco/mode_vegetation_type/ingest.json</t>
         </is>
       </c>
       <c r="F218" s="4" t="inlineStr">
         <is>
-          <t>decade season varname X Y</t>
+          <t>era model scenario X Y</t>
         </is>
       </c>
       <c r="G218" s="4" t="inlineStr">
         <is>
-          <t>10,4,2,3218,1186</t>
+          <t>4,6,4,3650,2100</t>
         </is>
       </c>
       <c r="H218" s="4" t="n">
@@ -30452,39 +30448,39 @@
       <c r="J218" s="4" t="inlineStr"/>
       <c r="K218" s="4" t="inlineStr">
         <is>
-          <t>[0:0,0:0,0:0,0:58099,0:17]</t>
+          <t>[0:0,0:0,0:0,0:65535,0:16]</t>
         </is>
       </c>
       <c r="L218" s="4" t="inlineStr">
         <is>
-          <t>1,1,1,3218,18</t>
+          <t>1,1,1,3650,17</t>
         </is>
       </c>
       <c r="M218" s="7" t="n">
-        <v>8276</v>
+        <v>11777</v>
       </c>
       <c r="N218" s="8" t="n">
-        <v>1.221</v>
+        <v>2.943</v>
       </c>
       <c r="O218" s="8" t="n">
-        <v>1.897</v>
+        <v>2.88</v>
       </c>
       <c r="P218" s="8" t="n">
-        <v>1.221</v>
+        <v>1.41</v>
       </c>
       <c r="Q218" s="9" t="n">
-        <v>1.5532</v>
+        <v>0.9786</v>
       </c>
       <c r="R218" s="8" t="n">
-        <v>0.676</v>
-      </c>
-      <c r="S218" s="12" t="inlineStr">
-        <is>
-          <t>duplicate entries</t>
+        <v>1.47</v>
+      </c>
+      <c r="S218" s="10" t="inlineStr">
+        <is>
+          <t>clean</t>
         </is>
       </c>
       <c r="T218" s="7" t="n">
-        <v>57924</v>
+        <v>62050</v>
       </c>
       <c r="U218" s="7" t="n">
         <v>1</v>
@@ -30495,18 +30491,18 @@
         </is>
       </c>
       <c r="W218" s="7" t="n">
-        <v>57924</v>
+        <v>62050</v>
       </c>
       <c r="X218" s="4" t="inlineStr">
         <is>
-          <t>ALIGNED [0:9, 0:3, 0:1, 0:113, 0:113] tile size 4158720</t>
+          <t>ALIGNED [0:3, 0:5, 0:3, 0:103, 0:103] tile size 4153344</t>
         </is>
       </c>
       <c r="Y218" s="7" t="n">
-        <v>12996</v>
+        <v>10816</v>
       </c>
       <c r="Z218" s="4" t="n">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="AA218" s="4" t="inlineStr">
         <is>
@@ -30539,17 +30535,17 @@
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
         <is>
-          <t>tas_2km_historical_wcs</t>
+          <t>iem_cru_2km_taspr_seasonal</t>
         </is>
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>tas_2km_historical_wcs</t>
+          <t>iem_cru_2km_taspr_seasonal</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>wcs</t>
+          <t>none</t>
         </is>
       </c>
       <c r="D219" s="4" t="inlineStr">
@@ -30557,51 +30553,55 @@
           <t>no</t>
         </is>
       </c>
-      <c r="E219" s="4" t="inlineStr"/>
+      <c r="E219" s="4" t="inlineStr">
+        <is>
+          <t>iem/tas_pr_2km/cru_seasonal_ingest.json</t>
+        </is>
+      </c>
       <c r="F219" s="4" t="inlineStr">
         <is>
-          <t>month year X Y</t>
+          <t>decade season varname X Y</t>
         </is>
       </c>
       <c r="G219" s="4" t="inlineStr">
         <is>
-          <t>12,115,1186,3218</t>
+          <t>10,4,2,3218,1186</t>
         </is>
       </c>
       <c r="H219" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I219" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J219" s="4" t="inlineStr"/>
       <c r="K219" s="4" t="inlineStr">
         <is>
-          <t>[0:11,0:114,0:31,0:31]</t>
+          <t>[0:0,0:0,0:0,0:58099,0:17]</t>
         </is>
       </c>
       <c r="L219" s="4" t="inlineStr">
         <is>
-          <t>1,1,31,31</t>
+          <t>1,1,1,3218,18</t>
         </is>
       </c>
       <c r="M219" s="7" t="n">
-        <v>276311</v>
+        <v>8276</v>
       </c>
       <c r="N219" s="8" t="n">
-        <v>63.202</v>
+        <v>1.221</v>
       </c>
       <c r="O219" s="8" t="n">
-        <v>238.46</v>
+        <v>1.897</v>
       </c>
       <c r="P219" s="8" t="n">
-        <v>63.202</v>
+        <v>1.221</v>
       </c>
       <c r="Q219" s="9" t="n">
-        <v>3.773</v>
+        <v>1.5532</v>
       </c>
       <c r="R219" s="8" t="n">
-        <v>175.258</v>
+        <v>0.676</v>
       </c>
       <c r="S219" s="12" t="inlineStr">
         <is>
@@ -30609,7 +30609,7 @@
         </is>
       </c>
       <c r="T219" s="7" t="n">
-        <v>961</v>
+        <v>57924</v>
       </c>
       <c r="U219" s="7" t="n">
         <v>1</v>
@@ -30620,18 +30620,18 @@
         </is>
       </c>
       <c r="W219" s="7" t="n">
-        <v>961</v>
+        <v>57924</v>
       </c>
       <c r="X219" s="4" t="inlineStr">
         <is>
-          <t>ALIGNED [0:11, 0:114, 0:14, 0:14] tile size 3726000</t>
+          <t>ALIGNED [0:9, 0:3, 0:1, 0:113, 0:113] tile size 4158720</t>
         </is>
       </c>
       <c r="Y219" s="7" t="n">
-        <v>225</v>
+        <v>12996</v>
       </c>
       <c r="Z219" s="4" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AA219" s="4" t="inlineStr">
         <is>
@@ -30657,7 +30657,7 @@
       </c>
       <c r="AG219" s="4" t="inlineStr">
         <is>
-          <t>sdom disagrees with DescribeCoverage extent; 7 distinct tile shapes in sample</t>
+          <t>7 distinct tile shapes in sample</t>
         </is>
       </c>
     </row>
@@ -30794,7 +30794,7 @@
       </c>
       <c r="AG220" s="4" t="inlineStr">
         <is>
-          <t>sdom disagrees with DescribeCoverage extent; 4 distinct tile shapes in sample</t>
+          <t>sdom disagrees with DescribeCoverage extent; 32 distinct tile shapes in sample</t>
         </is>
       </c>
     </row>
@@ -30931,7 +30931,7 @@
       </c>
       <c r="AG221" s="4" t="inlineStr">
         <is>
-          <t>sdom disagrees with DescribeCoverage extent; 6 distinct tile shapes in sample</t>
+          <t>sdom disagrees with DescribeCoverage extent; 56 distinct tile shapes in sample</t>
         </is>
       </c>
     </row>
@@ -33274,7 +33274,7 @@
       </c>
       <c r="L239" s="4" t="inlineStr">
         <is>
-          <t>9,2,637,1,1</t>
+          <t>9,3,637,1,1</t>
         </is>
       </c>
       <c r="M239" s="7" t="n">
@@ -33304,7 +33304,7 @@
         <v>1.6</v>
       </c>
       <c r="U239" s="7" t="n">
-        <v>11466</v>
+        <v>17199</v>
       </c>
       <c r="V239" s="4" t="inlineStr">
         <is>
@@ -33349,7 +33349,7 @@
       </c>
       <c r="AG239" s="4" t="inlineStr">
         <is>
-          <t>sdom disagrees with DescribeCoverage extent; 8 distinct tile shapes in sample</t>
+          <t>sdom disagrees with DescribeCoverage extent; 14 distinct tile shapes in sample</t>
         </is>
       </c>
     </row>
@@ -33486,7 +33486,7 @@
       </c>
       <c r="AG240" s="4" t="inlineStr">
         <is>
-          <t>collection name differs from coverage id; 7 distinct tile shapes in sample</t>
+          <t>collection name differs from coverage id; 10 distinct tile shapes in sample</t>
         </is>
       </c>
     </row>
@@ -33623,7 +33623,7 @@
       </c>
       <c r="AG241" s="4" t="inlineStr">
         <is>
-          <t>7 distinct tile shapes in sample</t>
+          <t>10 distinct tile shapes in sample</t>
         </is>
       </c>
     </row>
@@ -33760,7 +33760,7 @@
       </c>
       <c r="AG242" s="4" t="inlineStr">
         <is>
-          <t>7 distinct tile shapes in sample</t>
+          <t>10 distinct tile shapes in sample</t>
         </is>
       </c>
     </row>
@@ -33897,7 +33897,7 @@
       </c>
       <c r="AG243" s="4" t="inlineStr">
         <is>
-          <t>collection name differs from coverage id; 7 distinct tile shapes in sample</t>
+          <t>collection name differs from coverage id; 10 distinct tile shapes in sample</t>
         </is>
       </c>
     </row>
@@ -34034,7 +34034,7 @@
       </c>
       <c r="AG244" s="4" t="inlineStr">
         <is>
-          <t>collection name differs from coverage id; 7 distinct tile shapes in sample</t>
+          <t>collection name differs from coverage id; 10 distinct tile shapes in sample</t>
         </is>
       </c>
     </row>
@@ -34171,7 +34171,7 @@
       </c>
       <c r="AG245" s="4" t="inlineStr">
         <is>
-          <t>7 distinct tile shapes in sample</t>
+          <t>10 distinct tile shapes in sample</t>
         </is>
       </c>
     </row>
@@ -35685,7 +35685,11 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="AG257" s="4" t="inlineStr"/>
+      <c r="AG257" s="4" t="inlineStr">
+        <is>
+          <t>3 distinct tile shapes in sample</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="4" t="inlineStr">
@@ -39462,20 +39466,20 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>point query reads 682 x more than it returns</t>
+          <t>point query reads 570 x more than it returns</t>
         </is>
       </c>
       <c r="F41" s="8" t="n">
         <v>313.262</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>682.7</v>
+        <v>570.6</v>
       </c>
       <c r="H41" s="7" t="n">
         <v>49</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>13.9</v>
+        <v>11.6</v>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
@@ -47055,35 +47059,35 @@
       </c>
       <c r="B214" s="4" t="inlineStr">
         <is>
-          <t>alfresco_relative_flammability_30yr</t>
+          <t>tas_2km_historical_wcs</t>
         </is>
       </c>
       <c r="C214" s="4" t="inlineStr"/>
       <c r="D214" s="4" t="inlineStr">
         <is>
-          <t>alfresco_relative_flammability_30yr</t>
+          <t>tas_2km_historical_wcs</t>
         </is>
       </c>
       <c r="E214" s="4" t="inlineStr">
         <is>
-          <t>point query reads 62,050 x more than it returns</t>
+          <t>point query reads 1,905 x more than it returns</t>
         </is>
       </c>
       <c r="F214" s="8" t="n">
-        <v>1.717</v>
+        <v>63.202</v>
       </c>
       <c r="G214" s="7" t="n">
-        <v>62050</v>
+        <v>1905.3</v>
       </c>
       <c r="H214" s="7" t="n">
-        <v>7396</v>
+        <v>225</v>
       </c>
       <c r="I214" s="4" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J214" s="4" t="inlineStr">
         <is>
-          <t>ALIGNED [0:4, 0:6, 0:3, 0:85, 0:85] tile size 4141760</t>
+          <t>ALIGNED [0:11, 0:114, 0:14, 0:14] tile size 3726000</t>
         </is>
       </c>
     </row>
@@ -47095,35 +47099,35 @@
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>mean_annual_dtr</t>
+          <t>alfresco_relative_flammability_30yr</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr"/>
       <c r="D215" s="4" t="inlineStr">
         <is>
-          <t>mean_annual_dtr</t>
+          <t>alfresco_relative_flammability_30yr</t>
         </is>
       </c>
       <c r="E215" s="4" t="inlineStr">
         <is>
-          <t>point query reads 20,988 x more than it returns</t>
+          <t>point query reads 62,050 x more than it returns</t>
         </is>
       </c>
       <c r="F215" s="8" t="n">
-        <v>0.018</v>
+        <v>1.717</v>
       </c>
       <c r="G215" s="7" t="n">
-        <v>20988</v>
+        <v>62050</v>
       </c>
       <c r="H215" s="7" t="n">
-        <v>2809</v>
+        <v>7396</v>
       </c>
       <c r="I215" s="4" t="n">
-        <v>7.5</v>
+        <v>8.4</v>
       </c>
       <c r="J215" s="4" t="inlineStr">
         <is>
-          <t>ALIGNED [0:2, 0:120, 0:52, 0:52] tile size 4078668</t>
+          <t>ALIGNED [0:4, 0:6, 0:3, 0:85, 0:85] tile size 4141760</t>
         </is>
       </c>
     </row>
@@ -47135,35 +47139,35 @@
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>cmip6_indicators_cf_wms</t>
+          <t>mean_annual_dtr</t>
         </is>
       </c>
       <c r="C216" s="4" t="inlineStr"/>
       <c r="D216" s="4" t="inlineStr">
         <is>
-          <t>cmip6_indicators_cf_wms</t>
+          <t>mean_annual_dtr</t>
         </is>
       </c>
       <c r="E216" s="4" t="inlineStr">
         <is>
-          <t>map query reads 7 x more than it returns</t>
+          <t>point query reads 20,988 x more than it returns</t>
         </is>
       </c>
       <c r="F216" s="8" t="n">
-        <v>6.283</v>
+        <v>0.018</v>
       </c>
       <c r="G216" s="7" t="n">
-        <v>7</v>
+        <v>20988</v>
       </c>
       <c r="H216" s="7" t="n">
-        <v>1</v>
+        <v>2809</v>
       </c>
       <c r="I216" s="4" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="J216" s="4" t="inlineStr">
         <is>
-          <t>ALIGNED [0:0, 0:0, 0:0, 0:287, 0:42] tile size 594432</t>
+          <t>ALIGNED [0:2, 0:120, 0:52, 0:52] tile size 4078668</t>
         </is>
       </c>
     </row>
@@ -47175,35 +47179,35 @@
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>alfresco_vegetation_mode_statistic</t>
+          <t>cmip6_indicators_cf_wms</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr"/>
       <c r="D217" s="4" t="inlineStr">
         <is>
-          <t>alfresco_vegetation_mode_statistic</t>
+          <t>cmip6_indicators_cf_wms</t>
         </is>
       </c>
       <c r="E217" s="4" t="inlineStr">
         <is>
-          <t>point query reads 62,050 x more than it returns</t>
+          <t>map query reads 7 x more than it returns</t>
         </is>
       </c>
       <c r="F217" s="8" t="n">
-        <v>1.41</v>
+        <v>6.283</v>
       </c>
       <c r="G217" s="7" t="n">
-        <v>62050</v>
+        <v>7</v>
       </c>
       <c r="H217" s="7" t="n">
-        <v>10816</v>
+        <v>1</v>
       </c>
       <c r="I217" s="4" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="J217" s="4" t="inlineStr">
         <is>
-          <t>ALIGNED [0:3, 0:5, 0:3, 0:103, 0:103] tile size 4153344</t>
+          <t>ALIGNED [0:0, 0:0, 0:0, 0:287, 0:42] tile size 594432</t>
         </is>
       </c>
     </row>
@@ -47215,35 +47219,35 @@
       </c>
       <c r="B218" s="4" t="inlineStr">
         <is>
-          <t>iem_cru_2km_taspr_seasonal</t>
+          <t>alfresco_vegetation_mode_statistic</t>
         </is>
       </c>
       <c r="C218" s="4" t="inlineStr"/>
       <c r="D218" s="4" t="inlineStr">
         <is>
-          <t>iem_cru_2km_taspr_seasonal</t>
+          <t>alfresco_vegetation_mode_statistic</t>
         </is>
       </c>
       <c r="E218" s="4" t="inlineStr">
         <is>
-          <t>point query reads 57,924 x more than it returns</t>
+          <t>point query reads 62,050 x more than it returns</t>
         </is>
       </c>
       <c r="F218" s="8" t="n">
-        <v>1.221</v>
+        <v>1.41</v>
       </c>
       <c r="G218" s="7" t="n">
-        <v>57924</v>
+        <v>62050</v>
       </c>
       <c r="H218" s="7" t="n">
-        <v>12996</v>
+        <v>10816</v>
       </c>
       <c r="I218" s="4" t="n">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="J218" s="4" t="inlineStr">
         <is>
-          <t>ALIGNED [0:9, 0:3, 0:1, 0:113, 0:113] tile size 4158720</t>
+          <t>ALIGNED [0:3, 0:5, 0:3, 0:103, 0:103] tile size 4153344</t>
         </is>
       </c>
     </row>
@@ -47255,35 +47259,35 @@
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>tas_2km_historical_wcs</t>
+          <t>iem_cru_2km_taspr_seasonal</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr"/>
       <c r="D219" s="4" t="inlineStr">
         <is>
-          <t>tas_2km_historical_wcs</t>
+          <t>iem_cru_2km_taspr_seasonal</t>
         </is>
       </c>
       <c r="E219" s="4" t="inlineStr">
         <is>
-          <t>point query reads 961 x more than it returns</t>
+          <t>point query reads 57,924 x more than it returns</t>
         </is>
       </c>
       <c r="F219" s="8" t="n">
-        <v>63.202</v>
+        <v>1.221</v>
       </c>
       <c r="G219" s="7" t="n">
-        <v>961</v>
+        <v>57924</v>
       </c>
       <c r="H219" s="7" t="n">
-        <v>225</v>
+        <v>12996</v>
       </c>
       <c r="I219" s="4" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="J219" s="4" t="inlineStr">
         <is>
-          <t>ALIGNED [0:11, 0:114, 0:14, 0:14] tile size 3726000</t>
+          <t>ALIGNED [0:9, 0:3, 0:1, 0:113, 0:113] tile size 4158720</t>
         </is>
       </c>
     </row>

--- a/rasdaman_tiling_audit.xlsx
+++ b/rasdaman_tiling_audit.xlsx
@@ -526,7 +526,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>21 Sep 2026, corrected 22 Sep 2026 · 273 coverages · all measured directly · rasdaman v10.4.7</t>
+          <t>21 Sep 2026, corrected 22-23 Sep 2026 · 273 coverages · all measured directly · rasdaman v10.4.7</t>
         </is>
       </c>
     </row>
@@ -52268,7 +52268,7 @@
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>declared GB minus real disk GB. This is INDEX inflation from duplicate entries, confirmed to cost ~0 real bytes on disk for every coverage checked. Do not treat as reclaimable space.</t>
+          <t>declared GB minus real disk GB. Mostly index inflation from duplicate entries (Finding 1); a small share of it, on some coverages, is instead the separate, unexplained gap between logical size and PhysicalSize noted in Finding 1's caveats. Confirmed to cost ~0 real bytes on disk either way. Do not treat as reclaimable space.</t>
         </is>
       </c>
     </row>
